--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU13"/>
+  <dimension ref="A1:AU12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-06 21:00:00</t>
+          <t>2026-10-06 21:30:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2368,169 +2368,6 @@
         <v>0</v>
       </c>
       <c r="AU12" t="inlineStr">
-        <is>
-          <t>2026-10-06 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>-1</v>
-      </c>
-      <c r="AN13">
-        <v>-1</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>-1</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
         <is>
           <t>2026-10-06 21:35:00</t>
         </is>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G6">

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8">

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q10">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1948,55 +1948,55 @@
         <v>4.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O10">
         <v>3.4</v>
@@ -1978,10 +1978,10 @@
         <v>2.72</v>
       </c>
       <c r="AA10">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AB10">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AC10">
         <v>4.11</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.83</v>
+      </c>
+      <c r="O9">
+        <v>3.4</v>
+      </c>
+      <c r="P9">
+        <v>3.6</v>
+      </c>
+      <c r="Q9">
+        <v>2.55</v>
+      </c>
+      <c r="R9">
+        <v>2.28</v>
+      </c>
+      <c r="S9">
+        <v>1.4</v>
+      </c>
+      <c r="T9">
+        <v>2.65</v>
+      </c>
+      <c r="U9">
+        <v>2.6</v>
+      </c>
+      <c r="V9">
+        <v>1.4</v>
+      </c>
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.52</v>
+      </c>
+      <c r="AA9">
         <v>1.85</v>
       </c>
-      <c r="O9">
-        <v>3.6</v>
-      </c>
-      <c r="P9">
-        <v>4.14</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>2.05</v>
-      </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         <v>1.7</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P10">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q10">
         <v>2.48</v>
@@ -1954,10 +1954,10 @@
         <v>2.09</v>
       </c>
       <c r="S10">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
         <v>3.26</v>
@@ -2277,22 +2277,22 @@
         <v>10</v>
       </c>
       <c r="R12">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="AA12">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AG12">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>3.6</v>
       </c>
       <c r="AK12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1785,28 +1785,28 @@
         <v>3.6</v>
       </c>
       <c r="Q9">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R9">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U9">
         <v>2.6</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.26</v>
@@ -1815,10 +1815,10 @@
         <v>3.52</v>
       </c>
       <c r="AA9">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
         <v>2.98</v>
@@ -1830,10 +1830,10 @@
         <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="O10">
         <v>3.45</v>
       </c>
       <c r="P10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
         <v>2.48</v>
@@ -1978,10 +1978,10 @@
         <v>2.72</v>
       </c>
       <c r="AA10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB10">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC10">
         <v>4.11</v>
@@ -2283,7 +2283,7 @@
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
         <v>2.7</v>
@@ -2307,7 +2307,7 @@
         <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
         <v>3.2</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AK12">
         <v>1.06</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1785,10 +1785,10 @@
         <v>3.6</v>
       </c>
       <c r="Q9">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
         <v>1.38</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O10">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q10">
         <v>2.48</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
         <v>1.36</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1788,7 +1788,7 @@
         <v>2.55</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
         <v>1.38</v>
@@ -1806,13 +1806,13 @@
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="AA9">
         <v>1.9</v>
@@ -1821,19 +1821,19 @@
         <v>1.9</v>
       </c>
       <c r="AC9">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         <v>4.33</v>
       </c>
       <c r="Q10">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S10">
         <v>1.44</v>
@@ -1960,13 +1960,13 @@
         <v>2.62</v>
       </c>
       <c r="U10">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1978,7 +1978,7 @@
         <v>2.72</v>
       </c>
       <c r="AA10">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AB10">
         <v>1.6</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="P11">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q11">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
       <c r="R11">
         <v>2.5</v>
@@ -2120,13 +2120,13 @@
         <v>1.23</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U11">
         <v>2.16</v>
       </c>
       <c r="V11">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W11">
         <v>1.15</v>
@@ -2135,22 +2135,22 @@
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA11">
         <v>1.44</v>
       </c>
       <c r="AB11">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AC11">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AD11">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE11">
         <v>1.25</v>
@@ -2159,7 +2159,7 @@
         <v>1.4</v>
       </c>
       <c r="AG11">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1782,25 +1782,25 @@
         <v>3.4</v>
       </c>
       <c r="P9">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q9">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="R9">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
         <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U9">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V9">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
         <v>1.06</v>
@@ -1809,31 +1809,31 @@
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z9">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA9">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB9">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC9">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
         <v>1.76</v>
       </c>
       <c r="AG9">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="R10">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T10">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V10">
         <v>1.29</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>1.38</v>
+      </c>
+      <c r="Z10">
+        <v>2.62</v>
+      </c>
+      <c r="AA10">
+        <v>2.25</v>
+      </c>
+      <c r="AB10">
+        <v>1.59</v>
+      </c>
+      <c r="AC10">
+        <v>4</v>
+      </c>
+      <c r="AD10">
+        <v>1.17</v>
+      </c>
+      <c r="AE10">
         <v>1.02</v>
       </c>
-      <c r="Y10">
-        <v>1.43</v>
-      </c>
-      <c r="Z10">
-        <v>2.72</v>
-      </c>
-      <c r="AA10">
-        <v>2.24</v>
-      </c>
-      <c r="AB10">
-        <v>1.6</v>
-      </c>
-      <c r="AC10">
-        <v>4.11</v>
-      </c>
-      <c r="AD10">
-        <v>1.19</v>
-      </c>
-      <c r="AE10">
-        <v>1.01</v>
-      </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2310,10 +2310,10 @@
         <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.08</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK12">
         <v>1.03</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="Q2">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="U2">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
+        <v>1.06</v>
+      </c>
+      <c r="X2">
         <v>1.04</v>
       </c>
-      <c r="X2">
-        <v>1.01</v>
-      </c>
       <c r="Y2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC2">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
         <v>1.67</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G3">
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
+        <v>1.95</v>
+      </c>
+      <c r="O3">
+        <v>3.2</v>
+      </c>
+      <c r="P3">
+        <v>3.39</v>
+      </c>
+      <c r="Q3">
+        <v>2.64</v>
+      </c>
+      <c r="R3">
+        <v>2.02</v>
+      </c>
+      <c r="S3">
+        <v>1.38</v>
+      </c>
+      <c r="T3">
+        <v>2.64</v>
+      </c>
+      <c r="U3">
+        <v>2.8</v>
+      </c>
+      <c r="V3">
+        <v>1.34</v>
+      </c>
+      <c r="W3">
+        <v>1.04</v>
+      </c>
+      <c r="X3">
+        <v>1.01</v>
+      </c>
+      <c r="Y3">
+        <v>1.27</v>
+      </c>
+      <c r="Z3">
+        <v>3.14</v>
+      </c>
+      <c r="AA3">
         <v>1.92</v>
       </c>
-      <c r="O3">
-        <v>3.25</v>
-      </c>
-      <c r="P3">
-        <v>3.43</v>
-      </c>
-      <c r="Q3">
-        <v>2.5</v>
-      </c>
-      <c r="R3">
-        <v>2.1</v>
-      </c>
-      <c r="S3">
-        <v>1.36</v>
-      </c>
-      <c r="T3">
-        <v>2.8</v>
-      </c>
-      <c r="U3">
-        <v>2.75</v>
-      </c>
-      <c r="V3">
-        <v>1.36</v>
-      </c>
-      <c r="W3">
+      <c r="AB3">
+        <v>1.76</v>
+      </c>
+      <c r="AC3">
+        <v>3.28</v>
+      </c>
+      <c r="AD3">
+        <v>1.25</v>
+      </c>
+      <c r="AE3">
         <v>1.06</v>
       </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
-      <c r="Y3">
-        <v>1.29</v>
-      </c>
-      <c r="Z3">
-        <v>3.5</v>
-      </c>
-      <c r="AA3">
+      <c r="AF3">
+        <v>1.74</v>
+      </c>
+      <c r="AG3">
         <v>1.91</v>
       </c>
-      <c r="AB3">
-        <v>1.8</v>
-      </c>
-      <c r="AC3">
-        <v>3.4</v>
-      </c>
-      <c r="AD3">
-        <v>1.3</v>
-      </c>
-      <c r="AE3">
-        <v>1.1</v>
-      </c>
-      <c r="AF3">
-        <v>1.75</v>
-      </c>
-      <c r="AG3">
-        <v>1.93</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>1.67</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.27</v>
+        <v>1.41</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="P4">
-        <v>2.99</v>
+        <v>7.2</v>
       </c>
       <c r="Q4">
-        <v>3.06</v>
+        <v>1.98</v>
       </c>
       <c r="R4">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="U4">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z4">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AC4">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="AD4">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG4">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>1.55</v>
+        <v>2.46</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.72</v>
+        <v>2.27</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P5">
-        <v>3.8</v>
+        <v>2.99</v>
       </c>
       <c r="Q5">
-        <v>2.27</v>
+        <v>3.06</v>
       </c>
       <c r="R5">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T5">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="Z5">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AA5">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AB5">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AC5">
-        <v>2.49</v>
+        <v>3.74</v>
       </c>
       <c r="AD5">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK5">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="O6">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
-        <v>3.14</v>
+        <v>2.49</v>
       </c>
       <c r="AD6">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>2.27</v>
+      </c>
+      <c r="O4">
+        <v>2.9</v>
+      </c>
+      <c r="P4">
+        <v>2.99</v>
+      </c>
+      <c r="Q4">
+        <v>3.06</v>
+      </c>
+      <c r="R4">
+        <v>1.89</v>
+      </c>
+      <c r="S4">
         <v>1.41</v>
       </c>
-      <c r="O4">
-        <v>3.9</v>
-      </c>
-      <c r="P4">
-        <v>7.2</v>
-      </c>
-      <c r="Q4">
-        <v>1.98</v>
-      </c>
-      <c r="R4">
-        <v>2.16</v>
-      </c>
-      <c r="S4">
-        <v>1.36</v>
-      </c>
       <c r="T4">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="U4">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z4">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB4">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="AD4">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>2.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>1.72</v>
+      </c>
+      <c r="O5">
+        <v>3.5</v>
+      </c>
+      <c r="P5">
+        <v>3.8</v>
+      </c>
+      <c r="Q5">
         <v>2.27</v>
       </c>
-      <c r="O5">
-        <v>2.9</v>
-      </c>
-      <c r="P5">
-        <v>2.99</v>
-      </c>
-      <c r="Q5">
-        <v>3.06</v>
-      </c>
       <c r="R5">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="S5">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="U5">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="AA5">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AB5">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
-        <v>3.74</v>
+        <v>2.49</v>
       </c>
       <c r="AD5">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AE5">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P6">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q6">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="R6">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="AA6">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
-        <v>2.49</v>
+        <v>3.14</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK6">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -650,22 +650,22 @@
         <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T2">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
         <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.29</v>
@@ -692,7 +692,7 @@
         <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
         <v>1.95</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="Q3">
         <v>2.64</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P4">
         <v>2.99</v>
       </c>
       <c r="Q4">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="R4">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="U4">
         <v>2.9</v>
@@ -1000,13 +1000,13 @@
         <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AB4">
         <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AD4">
         <v>1.19</v>
@@ -1015,7 +1015,7 @@
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
         <v>1.91</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q5">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="R5">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
+        <v>1.27</v>
+      </c>
+      <c r="Z5">
+        <v>3.14</v>
+      </c>
+      <c r="AA5">
+        <v>2</v>
+      </c>
+      <c r="AB5">
+        <v>1.77</v>
+      </c>
+      <c r="AC5">
+        <v>3.14</v>
+      </c>
+      <c r="AD5">
+        <v>1.27</v>
+      </c>
+      <c r="AE5">
+        <v>1.07</v>
+      </c>
+      <c r="AF5">
+        <v>2.2</v>
+      </c>
+      <c r="AG5">
+        <v>1.62</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.17</v>
       </c>
-      <c r="Z5">
-        <v>4</v>
-      </c>
-      <c r="AA5">
-        <v>1.63</v>
-      </c>
-      <c r="AB5">
-        <v>2.1</v>
-      </c>
-      <c r="AC5">
-        <v>2.49</v>
-      </c>
-      <c r="AD5">
-        <v>1.42</v>
-      </c>
-      <c r="AE5">
-        <v>1.14</v>
-      </c>
-      <c r="AF5">
-        <v>1.57</v>
-      </c>
-      <c r="AG5">
-        <v>2.15</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.29</v>
-      </c>
       <c r="AK5">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="O6">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AC6">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AD6">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>1.62</v>
+        <v>2.19</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q9">
         <v>2.38</v>
@@ -1791,7 +1791,7 @@
         <v>2.14</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
         <v>2.97</v>
@@ -1815,7 +1815,7 @@
         <v>3.42</v>
       </c>
       <c r="AA9">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
         <v>1.86</v>
@@ -1833,7 +1833,7 @@
         <v>1.76</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>4.4</v>
+        <v>4.16</v>
       </c>
       <c r="Q10">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="R10">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="S10">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
         <v>3.4</v>
@@ -1966,37 +1966,37 @@
         <v>1.29</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z10">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA10">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB10">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AD10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
         <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2135,19 +2135,19 @@
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z11">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>1.44</v>
       </c>
       <c r="AB11">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="AC11">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AD11">
         <v>1.69</v>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R12">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2298,31 +2298,31 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="AG12">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q5">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AC5">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AD5">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF5">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>1.62</v>
+        <v>2.19</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P6">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="U6">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA6">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="AD6">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
+        <v>1.07</v>
+      </c>
+      <c r="AF6">
+        <v>2.2</v>
+      </c>
+      <c r="AG6">
+        <v>1.62</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.17</v>
       </c>
-      <c r="AF6">
-        <v>1.57</v>
-      </c>
-      <c r="AG6">
-        <v>2.19</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.3</v>
-      </c>
       <c r="AK6">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -659,7 +659,7 @@
         <v>2.7</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.08</v>
@@ -696,46 +696,46 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "76"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "54"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -807,10 +807,10 @@
         <v>3.25</v>
       </c>
       <c r="Q3">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="R3">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="S3">
         <v>1.38</v>
@@ -828,7 +828,7 @@
         <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
         <v>1.27</v>
@@ -837,68 +837,68 @@
         <v>3.14</v>
       </c>
       <c r="AA3">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC3">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
         <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="U4">
         <v>2.9</v>
@@ -1003,10 +1003,10 @@
         <v>2.19</v>
       </c>
       <c r="AB4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD4">
         <v>1.19</v>
@@ -1015,7 +1015,7 @@
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
         <v>1.91</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q5">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA5">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB5">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AC5">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="AD5">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AE5">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AG5">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="O6">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>7.2</v>
+        <v>3.29</v>
       </c>
       <c r="Q6">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AD6">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,14 +950,14 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5">
@@ -1120,68 +1120,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>7.2</v>
+        <v>3.29</v>
       </c>
       <c r="Q5">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AD5">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,37 +1194,37 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1255,16 +1255,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1276,118 +1276,118 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P6">
-        <v>3.29</v>
+        <v>7.2</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="U6">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA6">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
+        <v>1.77</v>
+      </c>
+      <c r="AC6">
+        <v>3.14</v>
+      </c>
+      <c r="AD6">
+        <v>1.27</v>
+      </c>
+      <c r="AE6">
+        <v>1.07</v>
+      </c>
+      <c r="AF6">
         <v>2.2</v>
       </c>
-      <c r="AC6">
-        <v>2.75</v>
-      </c>
-      <c r="AD6">
-        <v>1.4</v>
-      </c>
-      <c r="AE6">
-        <v>1.13</v>
-      </c>
-      <c r="AF6">
-        <v>1.57</v>
-      </c>
       <c r="AG6">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>["77"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1616,61 +1616,61 @@
         <v>2.7</v>
       </c>
       <c r="O8">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P8">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>

--- a/jogos_2026-10-06.xlsx
+++ b/jogos_2026-10-06.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8">
@@ -1619,7 +1619,7 @@
         <v>2.9</v>
       </c>
       <c r="P8">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
         <v>3.6</v>
@@ -1667,7 +1667,7 @@
         <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG8">
         <v>1.62</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O9">
         <v>3.25</v>
       </c>
       <c r="P9">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q9">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="R9">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
         <v>2.97</v>
@@ -1809,16 +1809,16 @@
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA9">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB9">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
         <v>3.14</v>
@@ -1830,26 +1830,26 @@
         <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG9">
+        <v>1.92</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.24</v>
+      </c>
+      <c r="AK9">
         <v>1.96</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.25</v>
-      </c>
-      <c r="AK9">
-        <v>1.89</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="O10">
         <v>3.25</v>
@@ -1948,40 +1948,40 @@
         <v>4.16</v>
       </c>
       <c r="Q10">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="R10">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S10">
         <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W10">
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y10">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z10">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AA10">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AB10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC10">
         <v>4.5</v>
@@ -1996,7 +1996,7 @@
         <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Q12">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AG12">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AL12">
         <v>0</v>
